--- a/Zinc/6. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -1128,10 +1128,10 @@
         <v>0.346153846153846</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E4" t="n">
-        <v>0.275280898876405</v>
+        <v>0.26123595505618</v>
       </c>
     </row>
     <row r="5">
@@ -1145,10 +1145,10 @@
         <v>0.0384615384615385</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E5" t="n">
-        <v>0.328651685393258</v>
+        <v>0.342696629213483</v>
       </c>
     </row>
     <row r="6">

--- a/Zinc/6. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Sample_ID</t>
   </si>
@@ -39,6 +39,9 @@
     <t xml:space="preserve">WaDE_64</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_65</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_67</t>
   </si>
   <si>
@@ -57,7 +60,7 @@
     <t xml:space="preserve">WaDE_187</t>
   </si>
   <si>
-    <t xml:space="preserve">WaDE_198</t>
+    <t xml:space="preserve">WaDE_193</t>
   </si>
   <si>
     <t xml:space="preserve">WaDE_234</t>
@@ -69,6 +72,12 @@
     <t xml:space="preserve">WaDE_315</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaDE_338</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_358</t>
   </si>
   <si>
@@ -87,6 +96,9 @@
     <t xml:space="preserve">WaDE_416</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_420</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_422</t>
   </si>
   <si>
@@ -96,12 +108,18 @@
     <t xml:space="preserve">WaDE_438</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_442</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_480</t>
   </si>
   <si>
     <t xml:space="preserve">WaDE_481</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_593</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_696</t>
   </si>
   <si>
@@ -126,16 +144,19 @@
     <t xml:space="preserve">prop_overall</t>
   </si>
   <si>
+    <t xml:space="preserve">Developed Tribs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Main Stem</t>
   </si>
   <si>
-    <t xml:space="preserve">NP Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD Tribs</t>
+    <t xml:space="preserve">Non-Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled Water</t>
   </si>
   <si>
     <t xml:space="preserve">BSL3.2</t>
@@ -144,6 +165,12 @@
     <t xml:space="preserve">BSL3.3</t>
   </si>
   <si>
+    <t xml:space="preserve">BSL4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">BSL5.1</t>
   </si>
   <si>
@@ -160,6 +187,9 @@
   </si>
   <si>
     <t xml:space="preserve">MCA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN2</t>
   </si>
   <si>
     <t xml:space="preserve">MTN4</t>
@@ -540,19 +570,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.45198735765686</v>
+        <v>-1.4545781512515</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0998999507939883</v>
+        <v>0.119357777506068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.44811850522937</v>
+        <v>0.501446033821061</v>
       </c>
       <c r="E2" t="n">
-        <v>0.113581027713599</v>
+        <v>0.104218291160888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00214422947892778</v>
+        <v>0.00243786084892092</v>
       </c>
     </row>
     <row r="3">
@@ -560,19 +590,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>2.41285370464409</v>
+        <v>2.31327532938492</v>
       </c>
       <c r="C3" t="n">
-        <v>0.107384111279476</v>
+        <v>0.252959707637803</v>
       </c>
       <c r="D3" t="n">
-        <v>0.512816895371491</v>
+        <v>1.12052267826532</v>
       </c>
       <c r="E3" t="n">
-        <v>0.217922744709906</v>
+        <v>0.194231019257194</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00610655549998581</v>
+        <v>0.0252213366973215</v>
       </c>
     </row>
     <row r="4">
@@ -580,19 +610,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>2.55906065108358</v>
+        <v>-0.392627631306215</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.913895219315977</v>
+        <v>-0.695629761671272</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.34233008383639</v>
+        <v>-3.08079782859642</v>
       </c>
       <c r="E4" t="n">
-        <v>0.209973979423785</v>
+        <v>0.193918313381599</v>
       </c>
       <c r="F4" t="n">
-        <v>0.417626938256222</v>
+        <v>0.190276398955525</v>
       </c>
     </row>
     <row r="5">
@@ -600,19 +630,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>-5.78681500940826</v>
+        <v>2.48192335580423</v>
       </c>
       <c r="C5" t="n">
-        <v>0.181840976201895</v>
+        <v>-0.797343575393041</v>
       </c>
       <c r="D5" t="n">
-        <v>0.869454164876966</v>
+        <v>-3.49304789512256</v>
       </c>
       <c r="E5" t="n">
-        <v>0.219838749865457</v>
+        <v>0.176182407518446</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0177513754053087</v>
+        <v>0.217449950582044</v>
       </c>
     </row>
     <row r="6">
@@ -620,19 +650,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>1.26707983347164</v>
+        <v>-5.79644808589717</v>
       </c>
       <c r="C6" t="n">
-        <v>1.04785267452245</v>
+        <v>0.176348063589626</v>
       </c>
       <c r="D6" t="n">
-        <v>4.66699487473519</v>
+        <v>0.789813596876793</v>
       </c>
       <c r="E6" t="n">
-        <v>0.10087503579176</v>
+        <v>0.211791120531229</v>
       </c>
       <c r="F6" t="n">
-        <v>0.203637167536325</v>
+        <v>0.013968005293628</v>
       </c>
     </row>
     <row r="7">
@@ -640,19 +670,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>1.32438608967945</v>
+        <v>1.24149955348726</v>
       </c>
       <c r="C7" t="n">
-        <v>0.664390181121367</v>
+        <v>1.11788573347637</v>
       </c>
       <c r="D7" t="n">
-        <v>2.87884701409374</v>
+        <v>4.65459978596709</v>
       </c>
       <c r="E7" t="n">
-        <v>0.050044001426758</v>
+        <v>0.0880326679721337</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0363834992025174</v>
+        <v>0.174280190853133</v>
       </c>
     </row>
     <row r="8">
@@ -660,19 +690,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.39826947040976</v>
+        <v>1.30377128052023</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0161065961630891</v>
+        <v>0.727004206609019</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0716284322969251</v>
+        <v>2.95827467159889</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0981570821463037</v>
+        <v>0.0451261459339174</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0000465350716359692</v>
+        <v>0.0344649764406929</v>
       </c>
     </row>
     <row r="9">
@@ -680,19 +710,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>2.60325297239594</v>
+        <v>-4.39986684319906</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.713765832223304</v>
+        <v>-0.0206787481845689</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.37751559394647</v>
+        <v>-0.0864192997174696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.203453681128008</v>
+        <v>0.0947341274392292</v>
       </c>
       <c r="F9" t="n">
-        <v>0.242810798248357</v>
+        <v>0.0000651284212166697</v>
       </c>
     </row>
     <row r="10">
@@ -700,19 +730,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>1.62868534845031</v>
+        <v>2.59209710647079</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0926037353757545</v>
+        <v>-0.661357668390382</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.405579847628207</v>
+        <v>-2.91613762904202</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0701807640484254</v>
+        <v>0.186784031923553</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00103464426509326</v>
+        <v>0.162767853387779</v>
       </c>
     </row>
     <row r="11">
@@ -720,19 +750,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>1.13860389119274</v>
+        <v>-0.279220051216797</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.566878939870201</v>
+        <v>-0.55052174482919</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.43227115420716</v>
+        <v>-2.32194069651438</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0311625486136995</v>
+        <v>0.111216766991839</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0158571371681552</v>
+        <v>0.0562205919609272</v>
       </c>
     </row>
     <row r="12">
@@ -740,19 +770,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.854444785802725</v>
+        <v>1.17047645334854</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.183615523774239</v>
+        <v>-0.56741228167962</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.821524012028852</v>
+        <v>-2.2882952336006</v>
       </c>
       <c r="E12" t="n">
-        <v>0.109010636384774</v>
+        <v>0.0278741394627505</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00688106456650328</v>
+        <v>0.0125118589016171</v>
       </c>
     </row>
     <row r="13">
@@ -760,19 +790,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>2.58453601337076</v>
+        <v>-0.811826844836716</v>
       </c>
       <c r="C13" t="n">
-        <v>0.65369672390477</v>
+        <v>-0.207004112383333</v>
       </c>
       <c r="D13" t="n">
-        <v>2.82621417894909</v>
+        <v>-0.862895444937987</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0458059006824599</v>
+        <v>0.0901061317438102</v>
       </c>
       <c r="F13" t="n">
-        <v>0.031953143975117</v>
+        <v>0.00614467212626882</v>
       </c>
     </row>
     <row r="14">
@@ -780,19 +810,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>2.13486544389335</v>
+        <v>2.58987589623574</v>
       </c>
       <c r="C14" t="n">
-        <v>0.70901281691605</v>
+        <v>0.699755294170245</v>
       </c>
       <c r="D14" t="n">
-        <v>3.07659176476142</v>
+        <v>2.8442125636365</v>
       </c>
       <c r="E14" t="n">
-        <v>0.052754224376966</v>
+        <v>0.042987898651538</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0439291768416503</v>
+        <v>0.0302810996079287</v>
       </c>
     </row>
     <row r="15">
@@ -800,19 +830,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>1.8755864671552</v>
+        <v>-0.607812293053791</v>
       </c>
       <c r="C15" t="n">
-        <v>0.257950022161725</v>
+        <v>-0.00280510857607255</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1769418463748</v>
+        <v>-0.0115606610532189</v>
       </c>
       <c r="E15" t="n">
-        <v>0.143247497892933</v>
+        <v>0.0691425907904241</v>
       </c>
       <c r="F15" t="n">
-        <v>0.019300138540054</v>
+        <v>0.000000827268673994622</v>
       </c>
     </row>
     <row r="16">
@@ -820,19 +850,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0438746723744532</v>
+        <v>-1.77874812012984</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0265128433750782</v>
+        <v>0.874839178788138</v>
       </c>
       <c r="D16" t="n">
-        <v>0.117428351786515</v>
+        <v>3.66814763743206</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0907968461903486</v>
+        <v>0.100684706513182</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000114755765538053</v>
+        <v>0.125534731368482</v>
       </c>
     </row>
     <row r="17">
@@ -840,19 +870,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>0.790547633965068</v>
+        <v>2.11505595730454</v>
       </c>
       <c r="C17" t="n">
-        <v>0.892815567293444</v>
+        <v>0.777254161793722</v>
       </c>
       <c r="D17" t="n">
-        <v>3.93758987149129</v>
+        <v>3.1683309479482</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0830264658048135</v>
+        <v>0.0484882013853385</v>
       </c>
       <c r="F17" t="n">
-        <v>0.11698750070719</v>
+        <v>0.042628664783778</v>
       </c>
     </row>
     <row r="18">
@@ -860,19 +890,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>2.08335316997618</v>
+        <v>1.85625933194215</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.209836254762269</v>
+        <v>0.320365355680463</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.963772958496303</v>
+        <v>1.3692391698232</v>
       </c>
       <c r="E18" t="n">
-        <v>0.154515149160697</v>
+        <v>0.134471034847516</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0141459937682108</v>
+        <v>0.0242730596869741</v>
       </c>
     </row>
     <row r="19">
@@ -880,19 +910,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>0.949123552181055</v>
+        <v>0.148012284661512</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.559191045635433</v>
+        <v>-0.050056939887433</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.41858266959602</v>
+        <v>-0.207444743475469</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0465612579352549</v>
+        <v>0.07939597675596</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0238052385089869</v>
+        <v>0.000309278158222732</v>
       </c>
     </row>
     <row r="20">
@@ -900,19 +930,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>1.25803879159611</v>
+        <v>0.906590202484115</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.31994418191558</v>
+        <v>0.816474696269582</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.55684350311517</v>
+        <v>3.37654008034933</v>
       </c>
       <c r="E20" t="n">
-        <v>0.277203988743928</v>
+        <v>0.0755343353343499</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3740170383782</v>
+        <v>0.0776276070303143</v>
       </c>
     </row>
     <row r="21">
@@ -920,19 +950,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>0.375456269594605</v>
+        <v>2.1540181505659</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.170240131433647</v>
+        <v>-0.23936907602463</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.776418463440406</v>
+        <v>-1.02056751592709</v>
       </c>
       <c r="E21" t="n">
-        <v>0.142515192144369</v>
+        <v>0.130235355910061</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00834920628280496</v>
+        <v>0.0129965890637837</v>
       </c>
     </row>
     <row r="22">
@@ -940,19 +970,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.62753262151694</v>
+        <v>0.99673114475698</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.930801945878017</v>
+        <v>-0.576826980707804</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.14475858751014</v>
+        <v>-2.33857583115701</v>
       </c>
       <c r="E22" t="n">
-        <v>0.100481009646023</v>
+        <v>0.0380835259650459</v>
       </c>
       <c r="F22" t="n">
-        <v>0.159915620599908</v>
+        <v>0.0180435279242528</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +990,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>0.483641790851008</v>
+        <v>0.0798191086878283</v>
       </c>
       <c r="C23" t="n">
-        <v>0.317425051825359</v>
+        <v>-0.540556495707221</v>
       </c>
       <c r="D23" t="n">
-        <v>1.44249423345204</v>
+        <v>-2.24567897640079</v>
       </c>
       <c r="E23" t="n">
-        <v>0.13632871926303</v>
+        <v>0.08391456321905</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0273706935147046</v>
+        <v>0.0384959870607074</v>
       </c>
     </row>
     <row r="24">
@@ -980,19 +1010,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0756745564725457</v>
+        <v>1.0612310354284</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.226836654429843</v>
+        <v>-1.09656379134173</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.06690742068312</v>
+        <v>-4.98239695047702</v>
       </c>
       <c r="E24" t="n">
-        <v>0.193754606023151</v>
+        <v>0.234156030216555</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0227959142443061</v>
+        <v>0.632499889022937</v>
       </c>
     </row>
     <row r="25">
@@ -1000,19 +1030,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>2.11828810049766</v>
+        <v>0.303597745394107</v>
       </c>
       <c r="C25" t="n">
-        <v>0.576211936212132</v>
+        <v>-0.0697995082570348</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5529113577432</v>
+        <v>-0.297690378982342</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0913695613048332</v>
+        <v>0.130790883563112</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0546140625330903</v>
+        <v>0.00111122384721093</v>
       </c>
     </row>
     <row r="26">
@@ -1020,19 +1050,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>1.0929987833589</v>
+        <v>-0.492173933977571</v>
       </c>
       <c r="C26" t="n">
-        <v>0.715927459451432</v>
+        <v>-1.05084512766693</v>
       </c>
       <c r="D26" t="n">
-        <v>3.10344090384897</v>
+        <v>-4.36902989540854</v>
       </c>
       <c r="E26" t="n">
-        <v>0.050827095991375</v>
+        <v>0.0853466241954341</v>
       </c>
       <c r="F26" t="n">
-        <v>0.042978937884124</v>
+        <v>0.148428942353548</v>
       </c>
     </row>
     <row r="27">
@@ -1040,19 +1070,139 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>3.64384922063869</v>
+        <v>3.00240197157546</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.257105737568332</v>
+        <v>-0.307926114212848</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.17372673401313</v>
+        <v>-1.31856203970384</v>
       </c>
       <c r="E27" t="n">
-        <v>0.144177312764565</v>
+        <v>0.137734419503782</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0193404190083622</v>
+        <v>0.0231430889027603</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.320852477536917</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.513278846672027</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.14769474140968</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0969521357014403</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0412677196937367</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.146265734059183</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.271526645518904</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.18582017072829</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.171034633601168</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0241770938289194</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.507025396819166</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.783916675825519</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.16928964338018</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0326913135150032</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0282884987036948</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2.12605338257177</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.615754790761457</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.55770891811947</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0836476288036011</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0497636372696553</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1.16557840367692</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.683994104761057</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.78192827181809</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0442110493281457</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0298317978472024</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.60398725985638</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.164728127734926</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.699076099390192</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.122118775812017</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.00566518822888255</v>
       </c>
     </row>
   </sheetData>
@@ -1068,376 +1218,444 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.230769230769231</v>
+        <v>0.03125</v>
       </c>
       <c r="D2" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.356741573033708</v>
+        <v>0.316062176165803</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.384615384615385</v>
+        <v>0.1875</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0393258426966292</v>
+        <v>0.329015544041451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.346153846153846</v>
+        <v>0.28125</v>
       </c>
       <c r="D4" t="n">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.26123595505618</v>
+        <v>0.0362694300518135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.28125</v>
       </c>
       <c r="D5" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E5" t="n">
-        <v>0.342696629213483</v>
+        <v>0.240932642487047</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.21875</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0308988764044944</v>
+        <v>0.077720207253886</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.03125</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0280898876404494</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.03125</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00280898876404494</v>
+        <v>0.0259067357512953</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.03125</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0308988764044944</v>
+        <v>0.0103626943005181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.192307692307692</v>
+        <v>0.03125</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0308988764044944</v>
+        <v>0.0103626943005181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.153846153846154</v>
+        <v>0.03125</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0112359550561798</v>
+        <v>0.00259067357512953</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.03125</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0112359550561798</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.15625</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0308988764044944</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.15625</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0308988764044944</v>
+        <v>0.0129533678756477</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
       <c r="E15" t="n">
-        <v>0.0168539325842697</v>
+        <v>0.0103626943005181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.03125</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0112359550561798</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.0625</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0280898876404494</v>
+        <v>0.00518134715025907</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.03125</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00842696629213483</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0384615384615385</v>
+        <v>0.09375</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0196629213483146</v>
+        <v>0.0155440414507772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="D20" t="n">
         <v>6</v>
       </c>
-      <c r="C20" t="n">
-        <v>0.230769230769231</v>
-      </c>
-      <c r="D20" t="n">
-        <v>119</v>
-      </c>
       <c r="E20" t="n">
-        <v>0.334269662921348</v>
+        <v>0.0155440414507772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.346153846153846</v>
+        <v>0.0625</v>
       </c>
       <c r="D21" t="n">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>0.303370786516854</v>
+        <v>0.0259067357512953</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.423076923076923</v>
+        <v>0.03125</v>
       </c>
       <c r="D22" t="n">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.362359550561798</v>
+        <v>0.0129533678756477</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0207253886010363</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>131</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.339378238341969</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D25" t="n">
+        <v>110</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.284974093264249</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="D26" t="n">
+        <v>145</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.375647668393782</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/6. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -144,19 +144,19 @@
     <t xml:space="preserve">prop_overall</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed Tribs</t>
+    <t xml:space="preserve">Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled Water</t>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">BSL3.2</t>
